--- a/artfynd/A 21187-2020 artfynd.xlsx
+++ b/artfynd/A 21187-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,6 +958,144 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>80100735</v>
+      </c>
+      <c r="B4" t="n">
+        <v>89783</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ej möjlig att validera</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläckfingersvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramaria sanguinea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrbyskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>681441</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6566313</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-09-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-09-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett kraftigt ex under en stor grov gran. Bestånd med grova granar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bestånd med grova granar.</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Kjell Hedberg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21187-2020 artfynd.xlsx
+++ b/artfynd/A 21187-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
